--- a/04_DESIGN_TABLES/DesignTable_5406C.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5406C.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -517,6 +517,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -824,24 +829,41 @@
           <t>5406-C-20</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.66</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>5406-C-20</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF female cap</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p67 table TFA-p067-t01 "5406-C PIPE CAP" row 5406-C-20 col "L LGTH" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 57.5, page verified) [Brennan = yes 2026-10-18] - overall cap length; mapping: TFA p66 5406-C drawing: L = whole closed cap, C HEX = cap hex (impact/F2b.json, certain role; Air-Way caps of the other sizes differ, 0/6); same-table check on today's base: 0/6 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5406-C-02 0.69 vs 0.563); C1HEX@HEX: Brennan TFA catalog p67 table TFA-p067-t01 "5406-C PIPE CAP" row 5406-C-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 57.5, page verified) [Brennan = yes 2026-10-18] - cap hex; mapping: TFA p66 5406-C drawing: L = whole closed cap, C HEX = cap hex (impact/F2b.json, certain role; Air-Way caps of the other sizes differ, 0/6); same-table check on today's base: 3/6 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 5406-C-06 0.88 vs 0.812); TAPDRILL@BORE: end library gen_straight2 FPT[20] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 1.48, FPT_P1 1.16 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; $PRP@Threads: thread text from the part-number dash, format of the built 5406C rows</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex from the Brennan TFA catalog p67 alone (Brennan caps are 0.11-0.36 shorter than the Air-Way caps built in this table); end wall L - P1 = 0.09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -852,6 +874,11 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>5406-C-20</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
